--- a/public/assets/foods_bulk_format.xlsx
+++ b/public/assets/foods_bulk_format.xlsx
@@ -1,182 +1,167 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
-  <si>
-    <t xml:space="preserve">Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CategoryId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SubCategoryId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UnitId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DiscountType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AvailableTimeStarts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AvailableTimeEnds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddOns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attributes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StoreId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ModuleId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recommended</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chicago Pizza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chicago pizza, also commonly referred to as deep-dish pizza, gets its name from the city it was invented in. During early 1900.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-08-21-6120bb67e9382.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[{"name":"Patty","type":"multi","min":"1","max":"2","required":"on","values":[{"label":"2","optionPrice":"20"},{"label":"3","optionPrice":"20"}]}]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">["6","7","8"]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">["1"]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baked Breaded Chicken</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baked Breaded Chicken is a mid-week dinner dream. Juicy, tender chicken, covered with a golden crunchy, delicious outer coating of bread crumbs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-08-21-6120c504a9cab.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:17:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18:18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">["7","8"]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">["2"]</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Image</t>
+  </si>
+  <si>
+    <t>CategoryId</t>
+  </si>
+  <si>
+    <t>SubCategoryId</t>
+  </si>
+  <si>
+    <t>UnitId</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>DiscountType</t>
+  </si>
+  <si>
+    <t>AvailableTimeStarts</t>
+  </si>
+  <si>
+    <t>AvailableTimeEnds</t>
+  </si>
+  <si>
+    <t>Variations</t>
+  </si>
+  <si>
+    <t>AddOns</t>
+  </si>
+  <si>
+    <t>Attributes</t>
+  </si>
+  <si>
+    <t>StoreId</t>
+  </si>
+  <si>
+    <t>ModuleId</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Veg</t>
+  </si>
+  <si>
+    <t>Recommended</t>
+  </si>
+  <si>
+    <t>Gst</t>
+  </si>
+  <si>
+    <t>Chicago Pizza</t>
+  </si>
+  <si>
+    <t>Chicago pizza, also commonly referred to as deep-dish pizza, gets its name from the city it was invented in. During early 1900.</t>
+  </si>
+  <si>
+    <t>2021-08-21-6120bb67e9382.png</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>20:15:00</t>
+  </si>
+  <si>
+    <t>[{"name":"Patty","type":"multi","min":"1","max":"2","required":"on","values":[{"label":"2","optionPrice":"20"},{"label":"3","optionPrice":"20"}]}]</t>
+  </si>
+  <si>
+    <t>["6","7","8"]</t>
+  </si>
+  <si>
+    <t>["1"]</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Baked Breaded Chicken</t>
+  </si>
+  <si>
+    <t>Baked Breaded Chicken is a mid-week dinner dream. Juicy, tender chicken, covered with a golden crunchy, delicious outer coating of bread crumbs.</t>
+  </si>
+  <si>
+    <t>2021-08-21-6120c504a9cab.png</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>percent</t>
+  </si>
+  <si>
+    <t>11:17:00</t>
+  </si>
+  <si>
+    <t>18:18:00</t>
+  </si>
+  <si>
+    <t>["7","8"]</t>
+  </si>
+  <si>
+    <t>["2"]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="3">
     <font>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -184,73 +169,246 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+  <a:themeElements>
+    <a:clrScheme name="Sheets">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="0000FF"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Sheets">
+      <a:majorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U106"/>
-  <sheetFormatPr defaultColWidth="8.5234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="26" width="8.56"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -314,132 +472,138 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>1712</v>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" ht="12.75" customHeight="1">
+      <c r="A2" s="1">
+        <v>1712.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>150</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>10</v>
+        <v>25</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>150.0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>10.0</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="R2" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="V2" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3" ht="12.75" customHeight="1">
+      <c r="A3" s="1">
+        <v>1713.0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>200.0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="R2" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="T2" s="1" t="s">
+      <c r="O3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="R3" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>1713</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="R3" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="U3" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -459,7 +623,7 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -479,7 +643,7 @@
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -498,9 +662,9 @@
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.75" customHeight="1"/>
+    <row r="8" ht="12.75" customHeight="1"/>
+    <row r="9" ht="12.75" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -519,7 +683,7 @@
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -539,7 +703,7 @@
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -558,7 +722,7 @@
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -578,7 +742,7 @@
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="12.75" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -598,7 +762,7 @@
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="12.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -619,7 +783,7 @@
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -639,7 +803,7 @@
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="12.75" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -659,7 +823,7 @@
       <c r="T16" s="1"/>
       <c r="U16" s="1"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="12.75" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -678,7 +842,7 @@
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="12.75" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -697,7 +861,7 @@
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="12.75" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -718,7 +882,7 @@
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="12.75" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -737,7 +901,7 @@
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="12.75" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -758,7 +922,7 @@
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="12.75" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -777,7 +941,7 @@
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="12.75" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -798,7 +962,7 @@
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" ht="12.75" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -817,7 +981,7 @@
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="12.75" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -837,7 +1001,7 @@
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" ht="12.75" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -856,7 +1020,7 @@
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -877,7 +1041,7 @@
       <c r="T27" s="1"/>
       <c r="U27" s="1"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -898,7 +1062,7 @@
       <c r="T28" s="1"/>
       <c r="U28" s="1"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" ht="12.75" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -917,7 +1081,7 @@
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -938,7 +1102,7 @@
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -958,7 +1122,7 @@
       <c r="T31" s="1"/>
       <c r="U31" s="1"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -977,7 +1141,7 @@
       <c r="T32" s="1"/>
       <c r="U32" s="1"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -998,7 +1162,7 @@
       <c r="T33" s="1"/>
       <c r="U33" s="1"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1019,7 +1183,7 @@
       <c r="T34" s="1"/>
       <c r="U34" s="1"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1039,7 +1203,7 @@
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1059,7 +1223,7 @@
       <c r="T36" s="1"/>
       <c r="U36" s="1"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1078,7 +1242,7 @@
       <c r="T37" s="1"/>
       <c r="U37" s="1"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1098,7 +1262,7 @@
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1117,7 +1281,7 @@
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1136,7 +1300,7 @@
       <c r="T40" s="1"/>
       <c r="U40" s="1"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -1155,7 +1319,7 @@
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -1175,7 +1339,7 @@
       <c r="T42" s="1"/>
       <c r="U42" s="1"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -1196,7 +1360,7 @@
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -1217,7 +1381,7 @@
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -1237,7 +1401,7 @@
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -1256,7 +1420,7 @@
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1276,7 +1440,7 @@
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -1296,7 +1460,7 @@
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -1315,7 +1479,7 @@
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" ht="12.75" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1334,7 +1498,7 @@
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" ht="12.75" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -1354,7 +1518,7 @@
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" ht="12.75" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -1374,7 +1538,7 @@
       <c r="T52" s="1"/>
       <c r="U52" s="1"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" ht="12.75" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -1393,7 +1557,7 @@
       <c r="T53" s="1"/>
       <c r="U53" s="1"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" ht="12.75" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -1412,7 +1576,7 @@
       <c r="T54" s="1"/>
       <c r="U54" s="1"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" ht="12.75" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -1431,7 +1595,7 @@
       <c r="T55" s="1"/>
       <c r="U55" s="1"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" ht="12.75" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -1451,7 +1615,7 @@
       <c r="T56" s="1"/>
       <c r="U56" s="1"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" ht="12.75" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -1470,7 +1634,7 @@
       <c r="T57" s="1"/>
       <c r="U57" s="1"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" ht="12.75" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -1491,7 +1655,7 @@
       <c r="T58" s="1"/>
       <c r="U58" s="1"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" ht="12.75" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -1511,7 +1675,7 @@
       <c r="T59" s="1"/>
       <c r="U59" s="1"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" ht="12.75" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -1530,7 +1694,7 @@
       <c r="T60" s="1"/>
       <c r="U60" s="1"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" ht="12.75" customHeight="1">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -1552,7 +1716,7 @@
       <c r="T61" s="1"/>
       <c r="U61" s="1"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" ht="12.75" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -1573,7 +1737,7 @@
       <c r="T62" s="1"/>
       <c r="U62" s="1"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" ht="12.75" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -1594,7 +1758,7 @@
       <c r="T63" s="1"/>
       <c r="U63" s="1"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" ht="12.75" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -1614,7 +1778,7 @@
       <c r="T64" s="1"/>
       <c r="U64" s="1"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" ht="12.75" customHeight="1">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -1634,7 +1798,7 @@
       <c r="T65" s="1"/>
       <c r="U65" s="1"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" ht="12.75" customHeight="1">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -1654,7 +1818,7 @@
       <c r="T66" s="1"/>
       <c r="U66" s="1"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" ht="12.75" customHeight="1">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -1674,7 +1838,7 @@
       <c r="T67" s="1"/>
       <c r="U67" s="1"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" ht="12.75" customHeight="1">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -1693,7 +1857,7 @@
       <c r="T68" s="1"/>
       <c r="U68" s="1"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" ht="12.75" customHeight="1">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -1712,7 +1876,7 @@
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" ht="12.75" customHeight="1">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -1732,7 +1896,7 @@
       <c r="T70" s="1"/>
       <c r="U70" s="1"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" ht="12.75" customHeight="1">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -1752,7 +1916,7 @@
       <c r="T71" s="1"/>
       <c r="U71" s="1"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" ht="12.75" customHeight="1">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -1772,7 +1936,7 @@
       <c r="T72" s="1"/>
       <c r="U72" s="1"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" ht="12.75" customHeight="1">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -1792,7 +1956,7 @@
       <c r="T73" s="1"/>
       <c r="U73" s="1"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" ht="12.75" customHeight="1">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -1812,7 +1976,7 @@
       <c r="T74" s="1"/>
       <c r="U74" s="1"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" ht="12.75" customHeight="1">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -1832,7 +1996,7 @@
       <c r="T75" s="1"/>
       <c r="U75" s="1"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" ht="12.75" customHeight="1">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -1852,7 +2016,7 @@
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" ht="12.75" customHeight="1">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -1872,7 +2036,7 @@
       <c r="T77" s="1"/>
       <c r="U77" s="1"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" ht="12.75" customHeight="1">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -1891,7 +2055,7 @@
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" ht="12.75" customHeight="1">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -1911,7 +2075,7 @@
       <c r="T79" s="1"/>
       <c r="U79" s="1"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" ht="12.75" customHeight="1">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -1930,7 +2094,7 @@
       <c r="T80" s="1"/>
       <c r="U80" s="1"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" ht="12.75" customHeight="1">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -1949,7 +2113,7 @@
       <c r="T81" s="1"/>
       <c r="U81" s="1"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" ht="12.75" customHeight="1">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -1968,7 +2132,7 @@
       <c r="T82" s="1"/>
       <c r="U82" s="1"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" ht="12.75" customHeight="1">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -1988,7 +2152,7 @@
       <c r="T83" s="1"/>
       <c r="U83" s="1"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" ht="12.75" customHeight="1">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -2008,7 +2172,7 @@
       <c r="T84" s="1"/>
       <c r="U84" s="1"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" ht="12.75" customHeight="1">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -2028,7 +2192,7 @@
       <c r="T85" s="1"/>
       <c r="U85" s="1"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" ht="12.75" customHeight="1">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -2049,7 +2213,7 @@
       <c r="T86" s="1"/>
       <c r="U86" s="1"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" ht="12.75" customHeight="1">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -2069,7 +2233,7 @@
       <c r="T87" s="1"/>
       <c r="U87" s="1"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" ht="12.75" customHeight="1">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -2089,7 +2253,7 @@
       <c r="T88" s="1"/>
       <c r="U88" s="1"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" ht="12.75" customHeight="1">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -2109,7 +2273,7 @@
       <c r="T89" s="1"/>
       <c r="U89" s="1"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" ht="12.75" customHeight="1">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -2128,7 +2292,7 @@
       <c r="T90" s="1"/>
       <c r="U90" s="1"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" ht="12.75" customHeight="1">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -2147,7 +2311,7 @@
       <c r="T91" s="1"/>
       <c r="U91" s="1"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" ht="12.75" customHeight="1">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -2166,7 +2330,7 @@
       <c r="T92" s="1"/>
       <c r="U92" s="1"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" ht="12.75" customHeight="1">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -2185,7 +2349,7 @@
       <c r="T93" s="1"/>
       <c r="U93" s="1"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" ht="12.75" customHeight="1">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -2205,7 +2369,7 @@
       <c r="T94" s="1"/>
       <c r="U94" s="1"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" ht="12.75" customHeight="1">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -2225,7 +2389,7 @@
       <c r="T95" s="1"/>
       <c r="U95" s="1"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" ht="12.75" customHeight="1">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -2244,7 +2408,7 @@
       <c r="T96" s="1"/>
       <c r="U96" s="1"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" ht="12.75" customHeight="1">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -2263,7 +2427,7 @@
       <c r="T97" s="1"/>
       <c r="U97" s="1"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" ht="12.75" customHeight="1">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -2284,7 +2448,7 @@
       <c r="T98" s="1"/>
       <c r="U98" s="1"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" ht="12.75" customHeight="1">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -2303,7 +2467,7 @@
       <c r="T99" s="1"/>
       <c r="U99" s="1"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" ht="12.75" customHeight="1">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -2323,7 +2487,7 @@
       <c r="T100" s="1"/>
       <c r="U100" s="1"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" ht="12.75" customHeight="1">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -2344,7 +2508,7 @@
       <c r="T101" s="1"/>
       <c r="U101" s="1"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" ht="12.75" customHeight="1">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -2366,7 +2530,7 @@
       <c r="T102" s="1"/>
       <c r="U102" s="1"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" ht="12.75" customHeight="1">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -2386,7 +2550,7 @@
       <c r="T103" s="1"/>
       <c r="U103" s="1"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" ht="12.75" customHeight="1">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -2407,7 +2571,7 @@
       <c r="T104" s="1"/>
       <c r="U104" s="1"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" ht="12.75" customHeight="1">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -2429,7 +2593,7 @@
       <c r="T105" s="1"/>
       <c r="U105" s="1"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" ht="12.75" customHeight="1">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -2449,13 +2613,904 @@
       <c r="T106" s="1"/>
       <c r="U106" s="1"/>
     </row>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
+    <row r="998" ht="12.75" customHeight="1"/>
+    <row r="999" ht="12.75" customHeight="1"/>
+    <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions/>
+  <pageMargins bottom="0.984027777777778" footer="0.0" header="0.0" left="0.747916666666667" right="0.747916666666667" top="0.984027777777778"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>